--- a/beyonce_rectification_analysis_grouped.xlsx
+++ b/beyonce_rectification_analysis_grouped.xlsx
@@ -4,10 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17340" windowHeight="9575"/>
+    <workbookView windowWidth="14531" windowHeight="9395" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="PD_2025-05-27_01-42-26" sheetId="1" r:id="rId1"/>
+    <sheet name="PSSR_2025-05-29_11-18-21" sheetId="2" r:id="rId2"/>
+    <sheet name="Secondary_2025-05-31_10-05-22" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="559">
   <si>
     <t>Datetime \ Event</t>
   </si>
@@ -93,6 +96,15 @@
   </si>
   <si>
     <t>Column2</t>
+  </si>
+  <si>
+    <t>Column3</t>
+  </si>
+  <si>
+    <t>pss</t>
+  </si>
+  <si>
+    <t>second</t>
   </si>
   <si>
     <t>1981-09-05_02-26-04 (13)</t>
@@ -146,7 +158,10 @@
     <t>if anything its this time</t>
   </si>
   <si>
-    <t>8empty</t>
+    <t>4O 1b</t>
+  </si>
+  <si>
+    <t>2g 2O</t>
   </si>
   <si>
     <t>1981-09-05_02-41-56 (5)</t>
@@ -205,7 +220,10 @@
     <t>also use to compare</t>
   </si>
   <si>
-    <t>6empty</t>
+    <t>2O 1b</t>
+  </si>
+  <si>
+    <t>3g 2O</t>
   </si>
   <si>
     <t>1981-09-05_02-57-24 (2)</t>
@@ -265,7 +283,10 @@
     <t>1g 3o</t>
   </si>
   <si>
-    <t>5empty</t>
+    <t>2O 2b</t>
+  </si>
+  <si>
+    <t>3g 1O</t>
   </si>
   <si>
     <t>1981-09-05_03-01-32 (19)</t>
@@ -325,7 +346,7 @@
     <t>VEN (c) 150 MC (r) (3.23')</t>
   </si>
   <si>
-    <t>4empty</t>
+    <t>1O 2b</t>
   </si>
   <si>
     <t>1981-09-05_02-17-24</t>
@@ -692,6 +713,12 @@
   </si>
   <si>
     <t>2g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1g 3O </t>
+  </si>
+  <si>
+    <t>6O 1b</t>
   </si>
   <si>
     <t>1981-09-05_02-19-00</t>
@@ -1348,6 +1375,941 @@
   <si>
     <t>JUP (d) 45 VEN (r) (3.66')
 POF (d) 60 H3 (r) (3.42')</t>
+  </si>
+  <si>
+    <t>MER (cp) 30 JUP (r) (1.89')
+VEN (dr) 180 IC (r) (5.54')</t>
+  </si>
+  <si>
+    <t>NNO (cr) 30 AS (r) (7.25')
+MON (cp) 0 JUP (r) (22.78')
+MON (dr) 150 NNO (r) (11.11')
+VEN (cp) 120 H3 (r) (10.35')</t>
+  </si>
+  <si>
+    <t>NNO (cp) 30 AS (r) (10.20')
+NNO (cr) 30 AS (r) (7.01')
+MON (cr) 60 NNO (r) (15.21')
+MON (dp) 90 JUP (r) (6.58')
+VEN (cp) 120 H3 (r) (7.79')</t>
+  </si>
+  <si>
+    <t>MER (cr) 90 NEP (r) (9.90')
+SAT (cr) 60 IC (r) (0.09')</t>
+  </si>
+  <si>
+    <t>JUP (cp) 0 SUN (r) (3.77')
+MER (cr) 60 MC (r) (6.87')
+MON (cr) 45 JUP (r) (12.91')
+VEN (cp) 120 URA (r) (11.21')</t>
+  </si>
+  <si>
+    <t>MAR (cr) 120 DS (r) (2.27')
+MON (dr) 120 VEN (r) (0.32')
+VEN (cr) 0 SUN (r) (5.67')</t>
+  </si>
+  <si>
+    <t>MER (cr) 30 MC (r) (5.08')</t>
+  </si>
+  <si>
+    <t>PLU (cp) 60 VEN (r) (4.48')
+PLU (dr) 120 DS (r) (11.67')</t>
+  </si>
+  <si>
+    <t>MAR (dp) 150 H3 (r) (1.86')
+MON (cr) 180 NNO (r) (15.86')
+PLU (dr) 90 SAT (r) (0.01')
+SAT (cp) 150 H6 (r) (3.56')</t>
+  </si>
+  <si>
+    <t>JUP (dr) 60 AS (r) (11.66')
+JUP (dr) 120 H3 (r) (2.70')
+JUP (dr) 45 VEN (r) (1.95')
+JUP (cp) 0 MON (r) (3.58')
+VEN (dr) 150 POF (r) (8.22')
+VEN (cp) 30 JUP (r) (4.18')</t>
+  </si>
+  <si>
+    <t>JUP (dr) 60 AS (r) (10.08')
+JUP (dr) 120 H3 (r) (4.28')
+JUP (dr) 45 VEN (r) (0.37')
+JUP (cp) 0 MON (r) (2.59')
+VEN (dr) 150 POF (r) (7.79')</t>
+  </si>
+  <si>
+    <t>NNO (dp) 30 JUP (r) (3.28')
+MON (dr) 150 H5 (r) (15.14')
+PLU (cp) 60 JUP (r) (4.36')
+URA (cr) 150 MON (r) (4.60')</t>
+  </si>
+  <si>
+    <t>NNO (dp) 30 JUP (r) (3.28')
+MON (dr) 150 H5 (r) (15.14')
+PLU (cp) 60 JUP (r) (4.36')
+URA (cr) 150 MON (r) (4.60')
+VEN (cr) 45 SUN (r) (4.88')</t>
+  </si>
+  <si>
+    <t>JUP (cp) 150 POF (r) (1.43')
+MER (dr) 30 JUP (r) (6.43')
+MON (cp) 30 VEN (r) (17.87')</t>
+  </si>
+  <si>
+    <t>MER (dp) 60 NNO (r) (2.30')
+MON (cp) 90 JUP (r) (16.34')</t>
+  </si>
+  <si>
+    <t>JUP (dr) 135 MON (r) (0.09')
+NNO (cp) 0 JUP (r) (2.80')
+MER (cp) 0 SUN (r) (6.75')
+MER (dp) 60 MC (r) (11.05')
+MON (cr) 0 MER (r) (17.95')
+VEN (dr) 30 NNO (r) (2.31')</t>
+  </si>
+  <si>
+    <t>JUP (cp) 135 MON (r) (7.43')
+MON (cr) 150 JUP (r) (17.40')
+VEN (dr) 60 JUP (r) (10.59')
+VEN (dr) 30 SUN (r) (11.75')
+VEN (dp) 60 JUP (r) (7.87')</t>
+  </si>
+  <si>
+    <t>MER (cr) 30 NNO (r) (3.46')
+MON (dp) 30 AS (r) (0.41')
+MON (cr) 150 MC (r) (7.98')
+VEN (dp) 60 MC (r) (6.33')
+VEN (cr) 45 SUN (r) (7.28')</t>
+  </si>
+  <si>
+    <t>1981-09-05_02-26-04</t>
+  </si>
+  <si>
+    <t>MON (cr) 180 URA (r) (22.35')
+URA (dr) 150 IC (r) (0.48')</t>
+  </si>
+  <si>
+    <t>PLU (dr) 60 DS (r) (3.14')</t>
+  </si>
+  <si>
+    <t>JUP (dr) 60 MC (r) (1.63')
+VEN (cp) 120 MON (r) (8.71')
+VEN (dp) 30 NNO (r) (10.58')</t>
+  </si>
+  <si>
+    <t>MER (dr) 60 NNO (r) (4.20')
+MON (cr) 180 JUP (r) (29.44')
+MON (dr) 150 URA (r) (16.79')
+VEN (cr) 30 JUP (r) (1.14')
+VEN (cr) 0 SUN (r) (1.42')
+VEN (cp) 120 MC (r) (7.84')</t>
+  </si>
+  <si>
+    <t>JUP (cp) 150 SUN (r) (3.56')
+VEN (cr) 30 H5 (r) (8.91')</t>
+  </si>
+  <si>
+    <t>MAR (dp) 45 H3 (r) (3.61')
+MER (dr) 90 NEP (r) (4.90')
+PLU (dr) 90 SAT (r) (3.13')</t>
+  </si>
+  <si>
+    <t>JUP (dp) 45 VEN (r) (11.18')</t>
+  </si>
+  <si>
+    <t>JUP (dp) 45 VEN (r) (9.55')</t>
+  </si>
+  <si>
+    <t>JUP (dp) 60 NNO (r) (11.84')
+NNO (dr) 30 JUP (r) (1.67')
+PLU (cp) 60 JUP (r) (8.84')
+URA (cp) 120 DS (r) (11.13')
+VEN (cr) 45 SUN (r) (4.14')</t>
+  </si>
+  <si>
+    <t>JUP (dp) 60 NNO (r) (11.84')
+NNO (dp) 0 SUN (r) (0.67')
+NNO (dr) 30 JUP (r) (1.67')
+PLU (cp) 60 JUP (r) (8.84')
+PLU (cp) 30 SUN (r) (6.27')
+URA (cp) 120 DS (r) (11.13')</t>
+  </si>
+  <si>
+    <t>VEN (cp) 30 JUP (r) (2.33')
+VEN (cp) 0 SUN (r) (0.23')</t>
+  </si>
+  <si>
+    <t>VEN (dp) 0 NNO (r) (7.06')</t>
+  </si>
+  <si>
+    <t>NNO (cp) 30 SUN (r) (1.15')
+NNO (cr) 0 JUP (r) (1.05')
+MON (cp) 180 AS (r) (3.38')
+MON (dp) 0 MC (r) (30.86')
+VEN (cp) 120 MON (r) (10.79')
+VEN (cp) 120 URA (r) (5.95')</t>
+  </si>
+  <si>
+    <t>MON (cr) 135 MER (r) (9.88')
+MON (dp) 135 VEN (r) (3.02')
+URA (cp) 150 DS (r) (9.95')
+URA (cr) 150 DS (r) (10.28')
+VEN (dp) 60 JUP (r) (11.01')
+VEN (dp) 30 SUN (r) (8.45')</t>
+  </si>
+  <si>
+    <t>MER (cr) 30 NNO (r) (4.27')</t>
+  </si>
+  <si>
+    <t>1981-09-05_02-41-56</t>
+  </si>
+  <si>
+    <t>MON (dp) 180 URA (r) (17.34')
+MON (cr) 150 DS (r) (15.61')</t>
+  </si>
+  <si>
+    <t>MON (dp) 0 MC (r) (13.85')</t>
+  </si>
+  <si>
+    <t>MAR (cp) 120 MC (r) (5.85')</t>
+  </si>
+  <si>
+    <t>JUP (cp) 135 AS (r) (3.72')
+MER (dp) 120 MC (r) (6.12')
+MON (dp) 30 MC (r) (17.24')
+VEN (cp) 120 MON (r) (1.53')
+VEN (dp) 30 NNO (r) (11.43')</t>
+  </si>
+  <si>
+    <t>MON (dr) 150 URA (r) (7.70')
+VEN (cr) 30 JUP (r) (0.45')
+VEN (cr) 0 SUN (r) (1.60')</t>
+  </si>
+  <si>
+    <t>MER (dr) 90 NEP (r) (3.73')
+MON (dr) 135 MC (r) (10.61')
+MON (cp) 60 NEP (r) (15.09')
+PLU (dr) 90 SAT (r) (3.21')</t>
+  </si>
+  <si>
+    <t>JUP (dp) 45 VEN (r) (11.82')
+MER (cr) 120 MC (r) (6.08')
+MON (dp) 0 H3 (r) (27.81')</t>
+  </si>
+  <si>
+    <t>JUP (dp) 45 VEN (r) (10.19')
+MER (cr) 60 IC (r) (7.61')</t>
+  </si>
+  <si>
+    <t>JUP (dp) 60 NNO (r) (11.67')
+NNO (dr) 30 JUP (r) (1.50')
+PLU (cp) 60 JUP (r) (8.95')
+VEN (cr) 0 DS (r) (8.26')
+VEN (cr) 45 SUN (r) (4.12')</t>
+  </si>
+  <si>
+    <t>JUP (dp) 60 NNO (r) (11.67')
+NNO (dp) 0 SUN (r) (1.35')
+NNO (dr) 30 JUP (r) (1.50')
+PLU (cp) 60 JUP (r) (8.95')
+PLU (cp) 30 SUN (r) (6.90')
+VEN (cr) 0 DS (r) (8.26')
+VEN (cr) 45 SUN (r) (4.12')</t>
+  </si>
+  <si>
+    <t>VEN (cp) 30 JUP (r) (2.87')
+VEN (cp) 0 SUN (r) (0.82')</t>
+  </si>
+  <si>
+    <t>MON (cp) 180 MC (r) (10.04')
+MON (dp) 60 H3 (r) (4.75')
+VEN (dp) 0 NNO (r) (7.81')</t>
+  </si>
+  <si>
+    <t>NNO (cr) 0 JUP (r) (1.22')
+NNO (cr) 30 SUN (r) (0.83')
+VEN (cp) 120 URA (r) (5.33')</t>
+  </si>
+  <si>
+    <t>NNO (dr) 0 AS (r) (8.70')
+MON (dp) 135 VEN (r) (10.74')
+VEN (dp) 60 JUP (r) (11.09')
+VEN (dp) 30 SUN (r) (9.04')
+VEN (cp) 135 AS (r) (0.81')</t>
+  </si>
+  <si>
+    <t>MER (dr) 60 H3 (r) (11.37')
+URA (cp) 120 MC (r) (0.99')
+URA (dp) 30 AS (r) (0.26')</t>
+  </si>
+  <si>
+    <t>1O 1b</t>
+  </si>
+  <si>
+    <t>1981-09-05_02-57-24</t>
+  </si>
+  <si>
+    <t>JUP (cp) 120 DS (r) (4.86')
+MON (dp) 180 URA (r) (9.76')</t>
+  </si>
+  <si>
+    <t>MAR (cr) 45 DS (r) (10.39')</t>
+  </si>
+  <si>
+    <t>VEN (cp) 120 MON (r) (5.48')</t>
+  </si>
+  <si>
+    <t>MON (dp) 90 JUP (r) (14.94')
+MON (dp) 60 SUN (r) (13.38')
+MON (dr) 150 URA (r) (1.15')
+VEN (cr) 30 JUP (r) (0.22')
+VEN (cr) 0 SUN (r) (1.78')</t>
+  </si>
+  <si>
+    <t>NNO (dr) 150 H3 (r) (6.84')</t>
+  </si>
+  <si>
+    <t>MAR (cr) 30 H3 (r) (7.66')
+MON (cp) 60 NEP (r) (7.15')
+PLU (dr) 90 SAT (r) (3.29')
+URA (dr) 135 MON (r) (11.32')</t>
+  </si>
+  <si>
+    <t>JUP (cr) 60 MC (r) (0.86')
+MON (cp) 45 H3 (r) (15.80')
+MON (dr) 120 JUP (r) (13.08')</t>
+  </si>
+  <si>
+    <t>JUP (dp) 45 VEN (r) (10.81')
+JUP (cr) 60 MC (r) (1.87')</t>
+  </si>
+  <si>
+    <t>JUP (dp) 60 NNO (r) (11.50')
+NNO (dp) 0 SUN (r) (2.01')
+NNO (dr) 30 JUP (r) (1.34')
+PLU (cp) 60 JUP (r) (9.06')
+PLU (cp) 30 SUN (r) (7.51')
+URA (cr) 150 MC (r) (11.46')
+VEN (cr) 45 SUN (r) (4.10')</t>
+  </si>
+  <si>
+    <t>JUP (dp) 60 NNO (r) (11.50')
+MAR (cp) 60 H5 (r) (5.67')
+NNO (dp) 0 SUN (r) (2.01')
+NNO (dr) 30 JUP (r) (1.34')
+PLU (cp) 60 JUP (r) (9.06')
+PLU (cp) 30 SUN (r) (7.51')
+URA (cr) 150 MC (r) (11.46')
+VEN (cr) 45 SUN (r) (4.10')</t>
+  </si>
+  <si>
+    <t>VEN (cp) 30 JUP (r) (3.40')
+VEN (cp) 0 SUN (r) (1.84')</t>
+  </si>
+  <si>
+    <t>VEN (dr) 30 H3 (r) (7.51')
+VEN (dp) 0 NNO (r) (8.54')</t>
+  </si>
+  <si>
+    <t>NNO (cr) 0 JUP (r) (1.38')
+VEN (cp) 120 URA (r) (4.73')</t>
+  </si>
+  <si>
+    <t>MON (dp) 135 MC (r) (15.23')
+VEN (dp) 60 JUP (r) (11.16')
+VEN (dp) 30 SUN (r) (9.61')</t>
+  </si>
+  <si>
+    <t>1981-09-05_03-01-32</t>
+  </si>
+  <si>
+    <t>MON (dp) 180 URA (r) (7.73')</t>
+  </si>
+  <si>
+    <t>JUP (dr) 135 H3 (r) (3.25')
+VEN (cp) 120 MON (r) (7.35')</t>
+  </si>
+  <si>
+    <t>NNO (cr) 30 MC (r) (0.50')
+MON (dp) 90 JUP (r) (12.67')
+MON (dp) 60 SUN (r) (11.25')
+VEN (cr) 30 JUP (r) (0.40')</t>
+  </si>
+  <si>
+    <t>MON (cp) 0 DS (r) (10.77')
+VEN (dp) 45 DS (r) (2.72')
+VEN (dp) 30 H5 (r) (7.91')</t>
+  </si>
+  <si>
+    <t>MAR (cp) 30 H3 (r) (0.93')
+MON (cp) 60 NEP (r) (5.03')
+NEP (dr) 120 DS (r) (5.55')
+SAT (dr) 45 H6 (r) (5.98')</t>
+  </si>
+  <si>
+    <t>MON (dr) 120 JUP (r) (10.79')</t>
+  </si>
+  <si>
+    <t>JUP (dp) 45 VEN (r) (10.98')</t>
+  </si>
+  <si>
+    <t>JUP (dp) 60 NNO (r) (11.45')
+NNO (dr) 30 JUP (r) (1.29')
+MON (dp) 0 DS (r) (19.31')
+PLU (cp) 60 JUP (r) (9.09')</t>
+  </si>
+  <si>
+    <t>JUP (dp) 60 NNO (r) (11.45')
+NNO (dp) 0 SUN (r) (2.18')
+NNO (dr) 30 JUP (r) (1.29')
+MON (dp) 0 DS (r) (19.31')
+PLU (cp) 60 JUP (r) (9.09')
+PLU (cp) 30 SUN (r) (7.67')
+VEN (cr) 45 SUN (r) (4.10')</t>
+  </si>
+  <si>
+    <t>MON (dr) 150 H3 (r) (7.08')
+VEN (cp) 30 JUP (r) (3.54')
+VEN (cp) 0 SUN (r) (2.12')</t>
+  </si>
+  <si>
+    <t>NNO (cr) 120 AS (r) (1.48')
+MON (cr) 0 H3 (r) (30.95')
+MON (cr) 30 NNO (r) (2.79')
+VEN (cr) 150 MC (r) (4.78')</t>
+  </si>
+  <si>
+    <t>NNO (cr) 0 JUP (r) (1.43')
+NNO (cr) 30 SUN (r) (0.00')
+MON (cp) 90 MC (r) (8.98')
+VEN (cp) 120 URA (r) (4.57')</t>
+  </si>
+  <si>
+    <t>MON (cp) 30 H3 (r) (11.55')
+VEN (dp) 60 JUP (r) (11.18')
+VEN (dp) 30 SUN (r) (9.76')</t>
+  </si>
+  <si>
+    <t>MER (cp) 60 H3 (r) (10.33')
+MER (cr) 30 NNO (r) (4.67')
+VEN (cr) 45 SUN (r) (8.41')</t>
+  </si>
+  <si>
+    <t>IC (p) 120 JUP (r) (0.43')
+MON (c) 30 PLU (r) (10.16')</t>
+  </si>
+  <si>
+    <t>JUP (c) 60 MC (r) (2.18')
+SUN (c) 60 VEN (r) (6.75')
+VEN (c) 30 MER (c) (4.28')</t>
+  </si>
+  <si>
+    <t>AS (p) 60 MON (p) (6.71')
+JUP (c) 60 MC (r) (1.41')
+MON (c) 150 SUN (c) (18.38')
+MON (c) 90 VEN (r) (15.89')
+SUN (c) 60 VEN (r) (2.49')
+VEN (c) 30 MER (c) (7.81')</t>
+  </si>
+  <si>
+    <t>DS (c) 90 MAR (c) (6.60')
+MON (p) 45 URA (r) (4.10')
+MON (c) 150 MAR (r) (25.03')
+SAT (p) 0 MON (p) (30.77')</t>
+  </si>
+  <si>
+    <t>H3 (c) 0 MON (c) (7.95')
+H3 (p) 60 URA (p) (9.43')
+MER (c) 0 SUN (c) (0.98')
+VEN (c) 45 AS (r) (5.01')</t>
+  </si>
+  <si>
+    <t>NNO (c) 120 MON (c) (27.39')
+MON (p) 30 JUP (r) (17.64')
+SUN (p) 120 IC (r) (8.95')</t>
+  </si>
+  <si>
+    <t>AS (c) 0 JUP (r) (1.19')
+H3 (c) 120 MER (c) (0.02')</t>
+  </si>
+  <si>
+    <t>URA (p) 30 MON (p) (19.50')</t>
+  </si>
+  <si>
+    <t>H12 (p) 45 NEP (r) (8.86')
+H3 (c) 45 PLU (r) (2.23')</t>
+  </si>
+  <si>
+    <t>H3 (c) 60 JUP (c) (6.27')</t>
+  </si>
+  <si>
+    <t>JUP (c) 45 MON (c) (22.19')
+JUP (p) 120 MON (p) (1.92')
+MON (c) 60 VEN (r) (28.95')</t>
+  </si>
+  <si>
+    <t>H5 (p) 135 URA (p) (0.62')
+MON (p) 135 VEN (r) (28.36')
+VEN (c) 45 PLU (r) (2.68')</t>
+  </si>
+  <si>
+    <t>H5 (p) 135 URA (p) (0.62')
+H5 (c) 150 MAR (c) (6.49')
+MON (p) 135 VEN (r) (28.36')
+VEN (c) 30 SUN (c) (0.64')
+VEN (p) 120 MAR (r) (1.25')</t>
+  </si>
+  <si>
+    <t>JUP (c) 90 H3 (r) (7.18')
+MC (c) 60 VEN (c) (8.06')
+VEN (p) 30 AS (r) (4.53')</t>
+  </si>
+  <si>
+    <t>AS (c) 0 MER (r) (10.73')
+AS (c) 30 VEN (c) (1.12')
+JUP (c) 90 H3 (r) (1.53')
+MC (c) 60 VEN (c) (9.58')
+VEN (c) 30 MER (r) (9.61')</t>
+  </si>
+  <si>
+    <t>H3 (p) 120 JUP (r) (10.38')
+JUP (c) 30 AS (r) (1.67')
+URA (p) 180 MON (p) (19.60')
+VEN (p) 120 MC (r) (10.53')</t>
+  </si>
+  <si>
+    <t>H3 (c) 150 MON (c) (21.24')
+JUP (p) 30 MON (r) (5.53')
+MER (p) 30 URA (r) (8.26')
+VEN (c) 30 NNO (r) (8.56')
+VEN (c) 120 MON (c) (22.18')</t>
+  </si>
+  <si>
+    <t>H3 (p) 150 MON (p) (11.88')
+VEN (p) 30 MON (r) (8.04')
+VEN (p) 30 URA (r) (3.20')</t>
+  </si>
+  <si>
+    <t>MC (p) 120 MER (r) (9.86')
+MON (c) 60 URA (r) (4.95')
+SUN (c) 60 H3 (r) (5.14')
+SUN (c) 60 VEN (r) (1.20')
+URA (c) 60 MON (c) (18.61')</t>
+  </si>
+  <si>
+    <t>JUP (p) 30 VEN (p) (10.11')
+MC (c) 30 MON (c) (27.17')
+MC (p) 120 MER (r) (5.99')
+SUN (c) 60 H3 (r) (0.88')
+SUN (c) 60 VEN (r) (3.06')</t>
+  </si>
+  <si>
+    <t>MAR (p) 60 MON (p) (10.17')
+SAT (c) 90 MON (c) (3.44')</t>
+  </si>
+  <si>
+    <t>VEN (c) 90 H3 (r) (10.19')</t>
+  </si>
+  <si>
+    <t>H5 (c) 0 MAR (c) (7.19')
+JUP (p) 30 MON (p) (14.18')
+MON (c) 45 VEN (r) (16.19')
+VEN (p) 30 DS (r) (5.81')</t>
+  </si>
+  <si>
+    <t>AS (c) 120 MON (c) (26.28')
+MON (c) 60 MC (r) (21.49')</t>
+  </si>
+  <si>
+    <t>DS (p) 0 MON (r) (7.71')
+DS (p) 0 URA (r) (2.87')
+H5 (c) 135 MON (r) (4.32')
+MON (c) 0 VEN (r) (12.69')</t>
+  </si>
+  <si>
+    <t>H3 (c) 135 SAT (c) (4.65')
+MC (c) 135 NNO (c) (5.19')
+MAR (c) 60 H6 (r) (9.00')
+MAR (p) 120 NEP (r) (0.89')
+MON (c) 90 NEP (r) (30.59')</t>
+  </si>
+  <si>
+    <t>AS (p) 180 VEN (p) (1.75')</t>
+  </si>
+  <si>
+    <t>AS (c) 135 VEN (r) (2.97')
+AS (p) 180 VEN (p) (0.91')</t>
+  </si>
+  <si>
+    <t>DS (p) 0 VEN (p) (7.48')
+H5 (c) 120 POF (c) (10.89')
+PLU (c) 0 DS (r) (0.34')
+VEN (c) 30 SUN (c) (7.02')</t>
+  </si>
+  <si>
+    <t>DS (p) 120 MAR (r) (3.84')
+DS (p) 0 VEN (p) (7.48')
+H5 (c) 120 POF (c) (10.89')
+PLU (c) 0 DS (r) (0.34')
+PLU (p) 60 MAR (p) (1.91')
+VEN (c) 30 SUN (c) (7.02')</t>
+  </si>
+  <si>
+    <t>JUP (p) 120 H3 (r) (1.70')
+JUP (p) 0 VEN (r) (5.63')
+JUP (p) 45 VEN (p) (10.23')</t>
+  </si>
+  <si>
+    <t>AS (p) 135 JUP (p) (5.00')
+H3 (c) 30 MON (c) (19.00')
+JUP (p) 0 VEN (r) (6.99')
+VEN (c) 30 MER (r) (2.33')
+VEN (p) 135 AS (r) (10.33')</t>
+  </si>
+  <si>
+    <t>JUP (c) 135 MON (c) (31.99')</t>
+  </si>
+  <si>
+    <t>JUP (c) 150 MON (c) (18.55')
+MC (p) 120 JUP (p) (9.67')
+NNO (c) 0 SUN (c) (1.09')
+MON (c) 45 H3 (r) (24.19')</t>
+  </si>
+  <si>
+    <t>H3 (p) 120 MON (r) (10.64')
+JUP (p) 180 AS (r) (5.07')
+MC (c) 135 MON (c) (3.14')
+MER (p) 0 SUN (p) (10.60')
+MON (c) 0 AS (r) (30.13')
+MON (c) 180 VEN (r) (29.27')
+VEN (c) 135 MC (r) (7.36')</t>
+  </si>
+  <si>
+    <t>MON (p) 150 H3 (r) (15.66')
+URA (p) 30 VEN (p) (10.71')
+VEN (p) 30 URA (r) (2.45')</t>
+  </si>
+  <si>
+    <t>MER (c) 60 H3 (r) (1.11')
+MON (p) 150 AS (r) (15.01')
+MON (c) 60 URA (r) (3.49')
+SUN (c) 60 VEN (r) (1.06')
+URA (p) 150 AS (r) (1.48')
+URA (p) 60 MON (p) (16.49')</t>
+  </si>
+  <si>
+    <t>JUP (p) 30 VEN (p) (9.49')
+MER (c) 60 H3 (r) (7.69')
+SUN (c) 60 VEN (r) (3.20')
+URA (c) 60 MON (c) (29.43')
+URA (p) 150 AS (r) (1.67')</t>
+  </si>
+  <si>
+    <t>MAR (p) 60 MON (p) (2.43')</t>
+  </si>
+  <si>
+    <t>JUP (p) 90 MC (r) (3.75')
+MC (c) 30 URA (c) (2.70')</t>
+  </si>
+  <si>
+    <t>JUP (p) 30 MON (p) (6.46')
+MON (p) 120 IC (r) (12.07')
+MON (c) 45 VEN (r) (9.07')</t>
+  </si>
+  <si>
+    <t>H3 (p) 180 MC (r) (1.92')
+MC (p) 120 JUP (r) (9.84')
+MC (p) 150 SUN (r) (7.78')
+MON (p) 60 SUN (p) (29.48')</t>
+  </si>
+  <si>
+    <t>MON (c) 0 VEN (r) (5.39')</t>
+  </si>
+  <si>
+    <t>H12 (p) 180 PLU (p) (8.57')
+MAR (p) 120 NEP (r) (1.29')
+MON (p) 135 H6 (r) (8.72')</t>
+  </si>
+  <si>
+    <t>AS (c) 120 POF (r) (6.87')
+MON (c) 120 AS (r) (31.81')</t>
+  </si>
+  <si>
+    <t>H5 (c) 30 MON (c) (2.56')
+H5 (p) 30 JUP (p) (6.19')
+MON (p) 135 DS (r) (26.91')</t>
+  </si>
+  <si>
+    <t>H5 (c) 30 MON (c) (2.56')
+H5 (p) 30 JUP (p) (6.19')
+IC (c) 45 MAR (r) (2.37')
+MON (p) 135 DS (r) (26.91')
+VEN (c) 30 SUN (c) (7.19')</t>
+  </si>
+  <si>
+    <t>AS (c) 150 JUP (c) (3.98')
+H3 (p) 90 MON (p) (30.55')
+H3 (p) 120 URA (r) (1.65')
+JUP (p) 0 VEN (r) (6.27')
+JUP (p) 45 VEN (p) (9.63')
+MON (c) 60 AS (r) (3.27')</t>
+  </si>
+  <si>
+    <t>AS (c) 150 SUN (c) (6.78')
+AS (p) 30 MON (p) (20.88')
+JUP (p) 0 VEN (r) (6.35')
+MC (c) 180 MON (c) (1.08')
+VEN (c) 30 MER (r) (2.15')</t>
+  </si>
+  <si>
+    <t>JUP (c) 135 MON (c) (22.59')</t>
+  </si>
+  <si>
+    <t>H3 (p) 0 NNO (r) (6.48')
+JUP (c) 150 MON (c) (27.87')
+NNO (c) 0 SUN (c) (0.42')</t>
+  </si>
+  <si>
+    <t>DS (c) 30 URA (r) (7.51')
+MON (c) 90 H3 (r) (15.08')
+VEN (p) 30 URA (r) (1.71')</t>
+  </si>
+  <si>
+    <t>AS (p) 120 MON (p) (5.06')
+SUN (c) 60 VEN (r) (0.92')
+URA (p) 60 MON (p) (8.40')</t>
+  </si>
+  <si>
+    <t>JUP (p) 30 VEN (p) (8.89')
+MON (p) 90 H3 (r) (3.61')
+SUN (c) 60 VEN (r) (3.34')
+URA (c) 60 MON (c) (21.20')</t>
+  </si>
+  <si>
+    <t>H3 (c) 135 PLU (c) (5.81')
+SAT (c) 90 MON (c) (12.56')</t>
+  </si>
+  <si>
+    <t>H3 (c) 135 VEN (r) (1.22')</t>
+  </si>
+  <si>
+    <t>JUP (p) 30 MON (p) (1.08')
+MON (p) 90 H5 (r) (27.01')
+MON (c) 45 VEN (r) (2.13')</t>
+  </si>
+  <si>
+    <t>AS (p) 120 MER (r) (4.17')
+H3 (p) 180 MC (r) (4.40')
+MON (p) 60 SUN (p) (22.52')</t>
+  </si>
+  <si>
+    <t>DS (c) 30 PLU (r) (2.95')
+MC (p) 45 MON (p) (20.28')
+MON (c) 90 MC (r) (31.78')
+MON (c) 0 VEN (r) (1.72')
+MON (p) 60 DS (r) (10.77')
+MON (p) 135 H5 (r) (1.10')</t>
+  </si>
+  <si>
+    <t>MAR (p) 120 NEP (r) (1.68')
+MON (c) 90 NEP (r) (13.82')
+NEP (c) 90 MON (c) (28.71')
+PLU (c) 30 MON (c) (1.39')</t>
+  </si>
+  <si>
+    <t>H3 (p) 120 URA (r) (9.82')
+MON (c) 60 H3 (r) (30.50')</t>
+  </si>
+  <si>
+    <t>H3 (p) 120 URA (r) (3.61')
+H3 (c) 90 MON (c) (10.70')</t>
+  </si>
+  <si>
+    <t>POF (c) 150 H5 (r) (2.25')
+VEN (c) 30 SUN (c) (7.35')</t>
+  </si>
+  <si>
+    <t>MON (p) 180 SUN (r) (30.99')
+POF (c) 150 H5 (r) (2.25')
+PLU (p) 60 MAR (p) (1.19')
+SUN (p) 60 H5 (r) (7.90')
+VEN (c) 30 SUN (c) (7.35')</t>
+  </si>
+  <si>
+    <t>JUP (p) 0 VEN (r) (6.89')
+JUP (p) 45 VEN (p) (9.06')
+MC (p) 60 MON (p) (9.87')
+MON (p) 150 URA (r) (22.60')
+URA (p) 150 H3 (r) (2.94')
+VEN (p) 45 SUN (p) (3.09')</t>
+  </si>
+  <si>
+    <t>JUP (p) 0 VEN (r) (5.73')
+MC (c) 150 POF (r) (6.68')
+MC (p) 90 MON (r) (3.19')
+VEN (c) 30 MER (r) (1.97')
+VEN (p) 45 SUN (p) (10.41')</t>
+  </si>
+  <si>
+    <t>H3 (c) 135 JUP (c) (2.22')
+H3 (c) 0 MON (c) (11.20')
+JUP (c) 135 MON (c) (13.42')
+JUP (p) 90 MC (r) (6.44')</t>
+  </si>
+  <si>
+    <t>AS (c) 60 MON (c) (25.65')
+H3 (p) 60 MER (r) (10.82')
+JUP (p) 90 MC (r) (6.62')</t>
+  </si>
+  <si>
+    <t>AS (c) 150 JUP (c) (10.04')
+H3 (p) 30 MON (p) (13.68')
+MON (c) 90 MC (r) (12.62')</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>tight orb</t>
+  </si>
+  <si>
+    <t>primary</t>
+  </si>
+  <si>
+    <t>SUN (c) 60 JUP (r) (4.92')</t>
+  </si>
+  <si>
+    <t>PLU (d) 90 H6 (r) (2.60')</t>
+  </si>
+  <si>
+    <t>3 tight orbs</t>
+  </si>
+  <si>
+    <t>8 empty</t>
+  </si>
+  <si>
+    <t>2 conj with angles</t>
+  </si>
+  <si>
+    <t>NNO (d) 60 H3 (r) (2.24')</t>
+  </si>
+  <si>
+    <t>URA (c) 0 VEN (r) (2.59')</t>
+  </si>
+  <si>
+    <t>MER (c) 0 H5 (r) (8.82')</t>
+  </si>
+  <si>
+    <t>DS (c) 0 SUN (r) (4.64')
+MER (c) 0 H5 (r) (8.82')</t>
+  </si>
+  <si>
+    <t>VEN (c) 60 H3 (r) (0.22')</t>
+  </si>
+  <si>
+    <t>4 tight orbs</t>
+  </si>
+  <si>
+    <t>9 empty</t>
+  </si>
+  <si>
+    <t>1 conj with angle</t>
+  </si>
+  <si>
+    <t>Secondaries</t>
+  </si>
+  <si>
+    <t>MER (c) 60 H3 (r) (1.11')
+MON (c) 60 URA (r) (3.49')
+SUN (c) 60 VEN (r) (1.06')
+URA (p) 60 MON (p) (16.49')</t>
+  </si>
+  <si>
+    <t>MER (c) 60 H3 (r) (7.69')
+SUN (c) 60 VEN (r) (3.20')
+URA (c) 60 MON (c) (29.43')</t>
+  </si>
+  <si>
+    <t>MON (p) 120 IC (r) (12.07')</t>
+  </si>
+  <si>
+    <t>MC (p) 120 JUP (r) (9.84')
+MON (p) 60 SUN (p) (29.48')</t>
+  </si>
+  <si>
+    <t>H12 (p) 180 PLU (p) (8.57')</t>
+  </si>
+  <si>
+    <t>H3 (p) 120 URA (r) (1.65')
+JUP (p) 0 VEN (r) (6.27')
+MON (c) 60 AS (r) (3.27')</t>
+  </si>
+  <si>
+    <t>JUP (p) 0 VEN (r) (6.35')</t>
+  </si>
+  <si>
+    <t>H3 (p) 0 NNO (r) (6.48')
+NNO (c) 0 SUN (c) (0.42')</t>
+  </si>
+  <si>
+    <t>2 tight orbs</t>
+  </si>
+  <si>
+    <t>2 conj 1 with angle</t>
+  </si>
+  <si>
+    <t>SUN (c) 60 VEN (r) (3.34')
+URA (c) 60 MON (c) (21.20')</t>
+  </si>
+  <si>
+    <t>SAT (c) 90 MON (c) (12.56')</t>
+  </si>
+  <si>
+    <t>AS (p) 120 MER (r) (4.17')
+MON (p) 60 SUN (p) (22.52')</t>
+  </si>
+  <si>
+    <t>MON (c) 0 VEN (r) (1.72')
+MON (p) 60 DS (r) (10.77')</t>
+  </si>
+  <si>
+    <t>MON (c) 90 NEP (r) (13.82')
+NEP (c) 90 MON (c) (28.71')</t>
+  </si>
+  <si>
+    <t>H3 (p) 120 URA (r) (3.61')</t>
+  </si>
+  <si>
+    <t>PLU (p) 60 MAR (p) (1.19')
+SUN (p) 60 H5 (r) (7.90')</t>
+  </si>
+  <si>
+    <t>JUP (p) 0 VEN (r) (6.89')
+MC (p) 60 MON (p) (9.87')</t>
+  </si>
+  <si>
+    <t>JUP (p) 0 VEN (r) (5.73')</t>
+  </si>
+  <si>
+    <t>H3 (c) 0 MON (c) (11.20')</t>
+  </si>
+  <si>
+    <t>AS (c) 60 MON (c) (25.65')
+H3 (p) 60 MER (r) (10.82')</t>
+  </si>
+  <si>
+    <t>1 tight</t>
+  </si>
+  <si>
+    <t>5 empty</t>
+  </si>
+  <si>
+    <t>1 conj with house</t>
   </si>
 </sst>
 </file>
@@ -1376,6 +2338,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1527,18 +2490,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1549,6 +2506,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1854,172 +2841,189 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="40" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2112,12 +3116,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:V26" totalsRowShown="0">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:V26" etc:filterBottomFollowUsedRange="0"/>
-  <sortState ref="A2:V26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:W26" totalsRowShown="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:W26" etc:filterBottomFollowUsedRange="0"/>
+  <sortState ref="A1:W26">
     <sortCondition ref="U1" descending="1"/>
   </sortState>
-  <tableColumns count="22">
+  <tableColumns count="23">
     <tableColumn id="1" name="Datetime \ Event" dataDxfId="0"/>
     <tableColumn id="2" name="BIRTH_SISTER 1986-06-24" dataDxfId="1"/>
     <tableColumn id="3" name="SUCCESS_ELECTED 2004-02-08"/>
@@ -2140,6 +3144,7 @@
     <tableColumn id="20" name="Column1"/>
     <tableColumn id="21" name="sum"/>
     <tableColumn id="22" name="Column2"/>
+    <tableColumn id="23" name="Column3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2430,14 +3435,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Z26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="19" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:22">
+    <row r="1" ht="28.8" customHeight="1" spans="1:26">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2504,1647 +3509,1688 @@
       <c r="V1" t="s">
         <v>21</v>
       </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="2" ht="72" spans="1:24">
-      <c r="A2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>23</v>
+    <row r="2" ht="72" customHeight="1" spans="1:26">
+      <c r="A2" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>27</v>
+        <v>27</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="G2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>32</v>
       </c>
       <c r="K2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="M2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="N2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>32</v>
+        <v>27</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="Q2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="S2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T2" s="9" t="s">
-        <v>33</v>
+        <v>27</v>
+      </c>
+      <c r="T2" s="18" t="s">
+        <v>36</v>
       </c>
       <c r="U2">
         <v>6</v>
       </c>
       <c r="V2" t="s">
-        <v>34</v>
-      </c>
-      <c r="X2" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="X2" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y2">
+        <v>5</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="3" ht="57.6" spans="1:24">
-      <c r="A3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>39</v>
+    <row r="3" ht="57.6" customHeight="1" spans="1:26">
+      <c r="A3" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>40</v>
+        <v>27</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="G3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>43</v>
+        <v>27</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="M3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>47</v>
+        <v>27</v>
+      </c>
+      <c r="N3" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="P3" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="R3" t="s">
-        <v>24</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="T3" s="9" t="s">
-        <v>49</v>
+        <v>27</v>
+      </c>
+      <c r="S3" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="T3" s="18" t="s">
+        <v>53</v>
       </c>
       <c r="U3">
         <v>5</v>
       </c>
       <c r="V3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="X3" t="s">
-        <v>51</v>
+        <v>55</v>
+      </c>
+      <c r="Y3">
+        <v>3</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="4" ht="72" spans="1:24">
-      <c r="A4" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>55</v>
+    <row r="4" ht="72" customHeight="1" spans="1:26">
+      <c r="A4" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>60</v>
+        <v>27</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="K4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="O4" s="6" t="s">
-        <v>63</v>
+        <v>27</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="N4" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>68</v>
       </c>
       <c r="P4" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q4" s="4" t="s">
-        <v>64</v>
+        <v>27</v>
+      </c>
+      <c r="Q4" s="12" t="s">
+        <v>69</v>
       </c>
       <c r="R4" t="s">
-        <v>24</v>
-      </c>
-      <c r="S4" s="5" t="s">
-        <v>65</v>
+        <v>27</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="T4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="U4">
         <v>4</v>
       </c>
       <c r="V4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="X4" t="s">
-        <v>67</v>
+        <v>72</v>
+      </c>
+      <c r="Y4">
+        <v>4</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>73</v>
       </c>
     </row>
-    <row r="5" ht="57.6" spans="1:24">
-      <c r="A5" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" s="4" t="s">
+    <row r="5" ht="57.6" customHeight="1" spans="1:25">
+      <c r="A5" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="M5" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="N5" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="O5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P5" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>27</v>
+      </c>
+      <c r="R5" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="S5" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="T5" t="s">
         <v>71</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="F5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="O5" t="s">
-        <v>24</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>24</v>
-      </c>
-      <c r="R5" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="S5" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="T5" t="s">
-        <v>66</v>
       </c>
       <c r="U5">
         <v>4</v>
       </c>
       <c r="V5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="X5" t="s">
-        <v>83</v>
+        <v>89</v>
+      </c>
+      <c r="Y5">
+        <v>3</v>
       </c>
     </row>
-    <row r="6" ht="57.6" spans="1:21">
+    <row r="6" ht="57.6" customHeight="1" spans="1:21">
       <c r="A6" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>87</v>
+        <v>27</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>93</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>88</v>
+        <v>27</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>94</v>
       </c>
       <c r="H6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>89</v>
+        <v>27</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>95</v>
       </c>
       <c r="J6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L6" t="s">
-        <v>24</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>92</v>
+        <v>27</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="O6" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="P6" s="12" t="s">
+        <v>98</v>
       </c>
       <c r="Q6" t="s">
-        <v>24</v>
-      </c>
-      <c r="R6" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="S6" s="5" t="s">
-        <v>94</v>
+        <v>27</v>
+      </c>
+      <c r="R6" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="S6" s="4" t="s">
+        <v>100</v>
       </c>
       <c r="T6" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="U6">
         <v>3</v>
       </c>
     </row>
-    <row r="7" ht="43.2" spans="1:21">
+    <row r="7" ht="43.2" customHeight="1" spans="1:21">
       <c r="A7" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>97</v>
+        <v>102</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>99</v>
+        <v>27</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>102</v>
+        <v>27</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>108</v>
       </c>
       <c r="M7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="N7" t="s">
-        <v>24</v>
-      </c>
-      <c r="O7" s="5" t="s">
-        <v>103</v>
+        <v>27</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>109</v>
       </c>
       <c r="P7" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q7" s="4" t="s">
-        <v>104</v>
+        <v>27</v>
+      </c>
+      <c r="Q7" s="12" t="s">
+        <v>110</v>
       </c>
       <c r="R7" t="s">
-        <v>24</v>
-      </c>
-      <c r="S7" s="4" t="s">
-        <v>105</v>
+        <v>27</v>
+      </c>
+      <c r="S7" s="12" t="s">
+        <v>111</v>
       </c>
       <c r="T7" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="U7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" ht="57.6" spans="1:21">
+    <row r="8" ht="57.6" customHeight="1" spans="1:21">
       <c r="A8" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>116</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>112</v>
+        <v>27</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>118</v>
       </c>
       <c r="H8" t="s">
-        <v>24</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="O8" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="P8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="12" t="s">
         <v>119</v>
       </c>
+      <c r="J8" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="L8" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="M8" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="N8" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="O8" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="P8" s="12" t="s">
+        <v>125</v>
+      </c>
       <c r="Q8" t="s">
-        <v>24</v>
-      </c>
-      <c r="R8" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="S8" s="4" t="s">
-        <v>121</v>
+        <v>27</v>
+      </c>
+      <c r="R8" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="S8" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="T8" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="U8">
         <v>3</v>
       </c>
     </row>
-    <row r="9" ht="43.2" spans="1:21">
+    <row r="9" ht="43.2" customHeight="1" spans="1:21">
       <c r="A9" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="G9" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="B9" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="C9" s="12" t="s">
         <v>131</v>
       </c>
+      <c r="D9" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="J9" t="s">
-        <v>24</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="N9" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="O9" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="R9" s="4" t="s">
+      <c r="L9" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="S9" s="4" t="s">
+      <c r="M9" s="12" t="s">
         <v>140</v>
       </c>
+      <c r="N9" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="P9" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q9" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="R9" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="S9" s="12" t="s">
+        <v>146</v>
+      </c>
       <c r="T9" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="U9">
         <v>3</v>
       </c>
     </row>
-    <row r="10" ht="43.2" spans="1:21">
+    <row r="10" ht="43.2" customHeight="1" spans="1:21">
       <c r="A10" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>144</v>
+        <v>147</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>150</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F10" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>145</v>
+        <v>27</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>151</v>
       </c>
       <c r="H10" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I10" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J10" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>150</v>
+        <v>27</v>
+      </c>
+      <c r="L10" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="M10" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="N10" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="O10" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="P10" s="12" t="s">
+        <v>156</v>
       </c>
       <c r="Q10" t="s">
-        <v>24</v>
-      </c>
-      <c r="R10" s="4" t="s">
-        <v>151</v>
+        <v>27</v>
+      </c>
+      <c r="R10" s="12" t="s">
+        <v>157</v>
       </c>
       <c r="S10" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="T10" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="U10">
         <v>3</v>
       </c>
     </row>
-    <row r="11" ht="43.2" spans="1:21">
+    <row r="11" ht="43.2" customHeight="1" spans="1:21">
       <c r="A11" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>153</v>
+        <v>158</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>159</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>154</v>
+        <v>27</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>160</v>
       </c>
       <c r="E11" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>157</v>
+        <v>27</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="J11" t="s">
-        <v>24</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="N11" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="O11" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="P11" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q11" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="R11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="S11" s="4" t="s">
+      <c r="L11" s="12" t="s">
         <v>165</v>
       </c>
+      <c r="M11" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="N11" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="O11" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="P11" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q11" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="R11" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="S11" s="12" t="s">
+        <v>171</v>
+      </c>
       <c r="T11" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="U11">
         <v>3</v>
       </c>
     </row>
-    <row r="12" ht="43.2" spans="1:21">
+    <row r="12" ht="43.2" customHeight="1" spans="1:26">
       <c r="A12" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="G12" s="4" t="s">
         <v>172</v>
       </c>
+      <c r="B12" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>178</v>
+      </c>
       <c r="H12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="N12" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="O12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" s="12" t="s">
         <v>179</v>
       </c>
+      <c r="J12" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="M12" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="N12" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="O12" s="12" t="s">
+        <v>185</v>
+      </c>
       <c r="P12" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q12" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="R12" s="4" t="s">
-        <v>181</v>
+        <v>27</v>
+      </c>
+      <c r="Q12" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="R12" s="12" t="s">
+        <v>187</v>
       </c>
       <c r="S12" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="T12" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="U12">
         <v>2</v>
       </c>
+      <c r="X12" t="s">
+        <v>189</v>
+      </c>
+      <c r="Y12">
+        <v>4</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>190</v>
+      </c>
     </row>
-    <row r="13" ht="86.4" spans="1:21">
+    <row r="13" ht="86.4" customHeight="1" spans="1:21">
       <c r="A13" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>187</v>
+        <v>191</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>195</v>
       </c>
       <c r="F13" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>190</v>
+        <v>27</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>198</v>
       </c>
       <c r="J13" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K13" t="s">
-        <v>24</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="N13" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="O13" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="P13" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q13" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="R13" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="S13" s="8" t="s">
-        <v>197</v>
+        <v>27</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="M13" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="N13" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="O13" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="P13" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q13" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="R13" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="S13" s="12" t="s">
+        <v>205</v>
       </c>
       <c r="T13" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="U13">
         <v>2</v>
       </c>
     </row>
-    <row r="14" ht="43.2" spans="1:21">
+    <row r="14" ht="43.2" customHeight="1" spans="1:21">
       <c r="A14" s="1" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>201</v>
+        <v>27</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>209</v>
       </c>
       <c r="F14" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G14" t="s">
-        <v>24</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>202</v>
+        <v>27</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>210</v>
       </c>
       <c r="I14" t="s">
-        <v>24</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="M14" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="K14" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="L14" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="M14" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="N14" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="O14" t="s">
+        <v>27</v>
+      </c>
+      <c r="P14" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q14" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="R14" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="S14" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="T14" t="s">
         <v>206</v>
-      </c>
-      <c r="N14" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="O14" t="s">
-        <v>24</v>
-      </c>
-      <c r="P14" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q14" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="R14" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="S14" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="T14" t="s">
-        <v>198</v>
       </c>
       <c r="U14">
         <v>2</v>
       </c>
     </row>
-    <row r="15" ht="72" spans="1:21">
+    <row r="15" ht="72" customHeight="1" spans="1:21">
       <c r="A15" s="1" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>213</v>
+        <v>27</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>221</v>
       </c>
       <c r="F15" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G15" t="s">
-        <v>24</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>214</v>
+        <v>27</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>222</v>
       </c>
       <c r="I15" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J15" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K15" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L15" t="s">
-        <v>24</v>
-      </c>
-      <c r="M15" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="N15" s="4" t="s">
-        <v>215</v>
+        <v>27</v>
+      </c>
+      <c r="M15" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="N15" s="12" t="s">
+        <v>223</v>
       </c>
       <c r="O15" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="P15" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q15" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="R15" s="6" t="s">
-        <v>217</v>
+        <v>27</v>
+      </c>
+      <c r="Q15" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="R15" s="5" t="s">
+        <v>225</v>
       </c>
       <c r="S15" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="T15" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="U15">
         <v>2</v>
       </c>
     </row>
-    <row r="16" ht="28.8" spans="1:21">
+    <row r="16" ht="28.8" customHeight="1" spans="1:21">
       <c r="A16" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>219</v>
+        <v>226</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>227</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>222</v>
+        <v>27</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>230</v>
       </c>
       <c r="H16" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I16" t="s">
-        <v>24</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>223</v>
+        <v>27</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>231</v>
       </c>
       <c r="K16" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L16" t="s">
-        <v>24</v>
-      </c>
-      <c r="M16" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="N16" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="O16" s="6" t="s">
-        <v>225</v>
+        <v>27</v>
+      </c>
+      <c r="M16" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="O16" s="5" t="s">
+        <v>233</v>
       </c>
       <c r="P16" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q16" s="4" t="s">
-        <v>226</v>
+        <v>27</v>
+      </c>
+      <c r="Q16" s="12" t="s">
+        <v>234</v>
       </c>
       <c r="R16" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="S16" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="T16" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="U16">
         <v>2</v>
       </c>
     </row>
-    <row r="17" ht="57.6" spans="1:21">
+    <row r="17" ht="57.6" customHeight="1" spans="1:21">
       <c r="A17" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>231</v>
+        <v>235</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>239</v>
       </c>
       <c r="F17" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>236</v>
+        <v>27</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="K17" s="12" t="s">
+        <v>244</v>
       </c>
       <c r="L17" t="s">
-        <v>24</v>
-      </c>
-      <c r="M17" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="N17" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="O17" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="P17" s="4" t="s">
-        <v>240</v>
+        <v>27</v>
+      </c>
+      <c r="M17" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="N17" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="O17" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="P17" s="12" t="s">
+        <v>248</v>
       </c>
       <c r="Q17" t="s">
-        <v>24</v>
-      </c>
-      <c r="R17" s="4" t="s">
-        <v>241</v>
+        <v>27</v>
+      </c>
+      <c r="R17" s="12" t="s">
+        <v>249</v>
       </c>
       <c r="S17" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="T17" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="U17">
         <v>2</v>
       </c>
     </row>
-    <row r="18" ht="100.8" spans="1:21">
+    <row r="18" ht="100.8" customHeight="1" spans="1:21">
       <c r="A18" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>244</v>
+        <v>251</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>252</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>246</v>
+        <v>27</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>254</v>
       </c>
       <c r="G18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="L18" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="M18" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="N18" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="O18" s="4" t="s">
-        <v>254</v>
+        <v>27</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="K18" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="L18" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="O18" s="12" t="s">
+        <v>262</v>
       </c>
       <c r="P18" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q18" s="4" t="s">
-        <v>255</v>
+        <v>27</v>
+      </c>
+      <c r="Q18" s="12" t="s">
+        <v>263</v>
       </c>
       <c r="R18" t="s">
-        <v>24</v>
-      </c>
-      <c r="S18" s="4" t="s">
-        <v>256</v>
+        <v>27</v>
+      </c>
+      <c r="S18" s="12" t="s">
+        <v>264</v>
       </c>
       <c r="T18" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="U18">
         <v>2</v>
       </c>
     </row>
-    <row r="19" ht="43.2" spans="1:21">
+    <row r="19" ht="43.2" customHeight="1" spans="1:21">
       <c r="A19" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>258</v>
+        <v>265</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>266</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>259</v>
+        <v>27</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>267</v>
       </c>
       <c r="F19" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G19" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H19" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I19" t="s">
-        <v>24</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>261</v>
+        <v>27</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="K19" s="12" t="s">
+        <v>269</v>
       </c>
       <c r="L19" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M19" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="N19" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="O19" t="s">
-        <v>24</v>
-      </c>
-      <c r="P19" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="Q19" s="4" t="s">
-        <v>263</v>
+        <v>27</v>
+      </c>
+      <c r="P19" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q19" s="12" t="s">
+        <v>271</v>
       </c>
       <c r="R19" t="s">
-        <v>24</v>
-      </c>
-      <c r="S19" s="4" t="s">
-        <v>264</v>
+        <v>27</v>
+      </c>
+      <c r="S19" s="12" t="s">
+        <v>272</v>
       </c>
       <c r="T19" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="U19">
         <v>1</v>
       </c>
     </row>
-    <row r="20" ht="43.2" spans="1:21">
+    <row r="20" ht="43.2" customHeight="1" spans="1:21">
       <c r="A20" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>268</v>
+        <v>274</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>276</v>
       </c>
       <c r="D20" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>270</v>
+        <v>27</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>278</v>
       </c>
       <c r="G20" t="s">
-        <v>24</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>271</v>
+        <v>27</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>279</v>
       </c>
       <c r="I20" t="s">
-        <v>24</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="L20" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="M20" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="N20" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="O20" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="P20" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="Q20" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="R20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J20" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="S20" s="4" t="s">
+      <c r="K20" s="12" t="s">
         <v>281</v>
       </c>
+      <c r="L20" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="M20" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="N20" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="O20" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="P20" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q20" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="R20" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="S20" s="12" t="s">
+        <v>289</v>
+      </c>
       <c r="T20" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="U20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" ht="57.6" spans="1:21">
+    <row r="21" ht="57.6" customHeight="1" spans="1:21">
       <c r="A21" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>284</v>
+        <v>291</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>292</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>288</v>
+        <v>27</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>296</v>
       </c>
       <c r="I21" t="s">
-        <v>24</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="K21" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="L21" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="M21" t="s">
+        <v>27</v>
+      </c>
+      <c r="N21" t="s">
+        <v>27</v>
+      </c>
+      <c r="O21" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="P21" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>27</v>
+      </c>
+      <c r="R21" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="S21" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="T21" t="s">
         <v>290</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="M21" t="s">
-        <v>24</v>
-      </c>
-      <c r="N21" t="s">
-        <v>24</v>
-      </c>
-      <c r="O21" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="P21" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>24</v>
-      </c>
-      <c r="R21" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="S21" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="T21" t="s">
-        <v>282</v>
       </c>
       <c r="U21">
         <v>1</v>
       </c>
     </row>
-    <row r="22" ht="43.2" spans="1:21">
+    <row r="22" ht="43.2" customHeight="1" spans="1:21">
       <c r="A22" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>299</v>
+        <v>304</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>307</v>
       </c>
       <c r="E22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="L22" s="4" t="s">
-        <v>306</v>
+        <v>27</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="I22" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="K22" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="L22" s="12" t="s">
+        <v>314</v>
       </c>
       <c r="M22" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="N22" t="s">
-        <v>24</v>
-      </c>
-      <c r="O22" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="P22" s="4" t="s">
-        <v>308</v>
+        <v>27</v>
+      </c>
+      <c r="O22" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="P22" s="12" t="s">
+        <v>316</v>
       </c>
       <c r="Q22" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R22" t="s">
-        <v>24</v>
-      </c>
-      <c r="S22" s="4" t="s">
-        <v>309</v>
+        <v>27</v>
+      </c>
+      <c r="S22" s="12" t="s">
+        <v>317</v>
       </c>
       <c r="T22" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="U22">
         <v>1</v>
       </c>
     </row>
-    <row r="23" ht="43.2" spans="1:21">
+    <row r="23" ht="43.2" customHeight="1" spans="1:21">
       <c r="A23" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>313</v>
+        <v>318</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>321</v>
       </c>
       <c r="E23" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F23" t="s">
-        <v>24</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>314</v>
+        <v>27</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>322</v>
       </c>
       <c r="H23" t="s">
-        <v>24</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>316</v>
+        <v>27</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>324</v>
       </c>
       <c r="K23" t="s">
-        <v>24</v>
-      </c>
-      <c r="L23" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="M23" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="N23" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="O23" s="4" t="s">
-        <v>319</v>
+        <v>27</v>
+      </c>
+      <c r="L23" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="M23" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="N23" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="O23" s="12" t="s">
+        <v>327</v>
       </c>
       <c r="P23" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q23" s="4" t="s">
-        <v>320</v>
+        <v>27</v>
+      </c>
+      <c r="Q23" s="12" t="s">
+        <v>328</v>
       </c>
       <c r="R23" t="s">
-        <v>24</v>
-      </c>
-      <c r="S23" s="4" t="s">
-        <v>321</v>
+        <v>27</v>
+      </c>
+      <c r="S23" s="12" t="s">
+        <v>329</v>
       </c>
       <c r="T23" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="U23">
         <v>1</v>
       </c>
     </row>
-    <row r="24" ht="57.6" spans="1:21">
+    <row r="24" ht="57.6" customHeight="1" spans="1:21">
       <c r="A24" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>323</v>
+        <v>330</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>331</v>
       </c>
       <c r="C24" t="s">
-        <v>24</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>326</v>
+        <v>27</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>334</v>
       </c>
       <c r="G24" t="s">
-        <v>24</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="K24" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="L24" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="M24" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="N24" s="4" t="s">
-        <v>333</v>
+        <v>27</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="I24" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="K24" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="L24" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="M24" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="N24" s="12" t="s">
+        <v>341</v>
       </c>
       <c r="O24" t="s">
-        <v>24</v>
-      </c>
-      <c r="P24" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="Q24" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="R24" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="S24" s="4" t="s">
-        <v>337</v>
+        <v>27</v>
+      </c>
+      <c r="P24" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q24" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="R24" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="S24" s="12" t="s">
+        <v>345</v>
       </c>
       <c r="T24" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="U24">
         <v>1</v>
       </c>
     </row>
-    <row r="25" ht="43.2" spans="1:21">
+    <row r="25" ht="43.2" customHeight="1" spans="1:21">
       <c r="A25" s="1" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>341</v>
+        <v>27</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>349</v>
       </c>
       <c r="F25" t="s">
-        <v>24</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>343</v>
+        <v>27</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>351</v>
       </c>
       <c r="I25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>345</v>
+        <v>27</v>
+      </c>
+      <c r="J25" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="K25" s="12" t="s">
+        <v>353</v>
       </c>
       <c r="L25" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M25" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="N25" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="O25" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="P25" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q25" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="R25" s="8" t="s">
-        <v>347</v>
+        <v>27</v>
+      </c>
+      <c r="Q25" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="R25" s="12" t="s">
+        <v>355</v>
       </c>
       <c r="S25" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="U25">
         <v>0</v>
       </c>
     </row>
-    <row r="26" ht="57.6" spans="1:21">
+    <row r="26" ht="57.6" customHeight="1" spans="1:21">
       <c r="A26" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>351</v>
+        <v>356</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>359</v>
       </c>
       <c r="E26" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F26" t="s">
-        <v>24</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>352</v>
+        <v>27</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>360</v>
       </c>
       <c r="H26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>354</v>
+        <v>27</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>362</v>
       </c>
       <c r="K26" t="s">
-        <v>24</v>
-      </c>
-      <c r="L26" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="M26" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="N26" s="4" t="s">
-        <v>356</v>
+        <v>27</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="M26" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="N26" s="12" t="s">
+        <v>364</v>
       </c>
       <c r="O26" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="P26" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Q26" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R26" t="s">
-        <v>24</v>
-      </c>
-      <c r="S26" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="T26"/>
+        <v>27</v>
+      </c>
+      <c r="S26" s="12" t="s">
+        <v>365</v>
+      </c>
       <c r="U26">
         <v>0</v>
       </c>
@@ -4156,4 +5202,1132 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:U6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="19" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28.8" customHeight="1" spans="1:19">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" ht="86.4" customHeight="1" spans="1:21">
+      <c r="A2" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="O2" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="T2" t="s">
+        <v>189</v>
+      </c>
+      <c r="U2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" ht="100.8" customHeight="1" spans="1:21">
+      <c r="A3" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="12"/>
+      <c r="E3" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="H3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="K3" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="M3" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="N3" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="O3" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="P3" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="Q3" s="15" t="s">
+        <v>397</v>
+      </c>
+      <c r="R3" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="S3" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="T3" t="s">
+        <v>38</v>
+      </c>
+      <c r="U3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" ht="100.8" customHeight="1" spans="1:21">
+      <c r="A4" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="L4" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="M4" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="N4" s="12" t="s">
+        <v>410</v>
+      </c>
+      <c r="O4" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="P4" s="15" t="s">
+        <v>412</v>
+      </c>
+      <c r="Q4" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="R4" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="T4" t="s">
+        <v>416</v>
+      </c>
+      <c r="U4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" ht="115.2" customHeight="1" spans="1:21">
+      <c r="A5" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>421</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="I5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="M5" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="N5" s="12" t="s">
+        <v>427</v>
+      </c>
+      <c r="O5" s="12" t="s">
+        <v>428</v>
+      </c>
+      <c r="P5" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="Q5" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="R5" s="12" t="s">
+        <v>431</v>
+      </c>
+      <c r="S5" t="s">
+        <v>27</v>
+      </c>
+      <c r="T5" t="s">
+        <v>72</v>
+      </c>
+      <c r="U5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" ht="100.8" customHeight="1" spans="1:21">
+      <c r="A6" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>433</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="H6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>436</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="N6" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="O6" s="12" t="s">
+        <v>442</v>
+      </c>
+      <c r="P6" s="12" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q6" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="R6" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="S6" s="12" t="s">
+        <v>446</v>
+      </c>
+      <c r="T6" t="s">
+        <v>89</v>
+      </c>
+      <c r="U6">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:T5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="19" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28.8" spans="1:19">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" ht="86.4" spans="1:20">
+      <c r="A2" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>450</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>451</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>452</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>455</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>456</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>457</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>458</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="O2" s="12" t="s">
+        <v>460</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>463</v>
+      </c>
+      <c r="S2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="3" ht="100.8" spans="1:20">
+      <c r="A3" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>464</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>467</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>472</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>473</v>
+      </c>
+      <c r="L3" s="14" t="s">
+        <v>474</v>
+      </c>
+      <c r="M3" s="12" t="s">
+        <v>475</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="P3" s="12" t="s">
+        <v>478</v>
+      </c>
+      <c r="Q3" s="12" t="s">
+        <v>479</v>
+      </c>
+      <c r="R3" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="S3" s="12" t="s">
+        <v>481</v>
+      </c>
+      <c r="T3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" ht="86.4" spans="1:20">
+      <c r="A4" s="13" t="s">
+        <v>400</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>482</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>485</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>488</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>489</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>490</v>
+      </c>
+      <c r="K4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="P4" s="14" t="s">
+        <v>495</v>
+      </c>
+      <c r="Q4" s="12" t="s">
+        <v>496</v>
+      </c>
+      <c r="R4" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="S4" t="s">
+        <v>27</v>
+      </c>
+      <c r="T4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" ht="86.4" spans="1:20">
+      <c r="A5" s="13" t="s">
+        <v>417</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>498</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>499</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>500</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>501</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>502</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>503</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>505</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>506</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>507</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="P5" s="12" t="s">
+        <v>512</v>
+      </c>
+      <c r="Q5" s="12" t="s">
+        <v>513</v>
+      </c>
+      <c r="R5" s="12" t="s">
+        <v>514</v>
+      </c>
+      <c r="S5" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="T5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:Z7"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="6"/>
+  <cols>
+    <col min="1" max="19" width="24.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28.8" customHeight="1" spans="1:23">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>516</v>
+      </c>
+      <c r="U1" t="s">
+        <v>517</v>
+      </c>
+      <c r="V1" t="s">
+        <v>518</v>
+      </c>
+      <c r="W1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="2" ht="28.8" customHeight="1" spans="1:19">
+      <c r="A2" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+    </row>
+    <row r="3" ht="57.6" customHeight="1" spans="1:26">
+      <c r="A3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>521</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="S3" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="T3" s="10">
+        <v>2</v>
+      </c>
+      <c r="U3" s="7">
+        <v>4</v>
+      </c>
+      <c r="V3" s="7"/>
+      <c r="W3" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="X3" s="7"/>
+      <c r="Y3" t="s">
+        <v>524</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="4" ht="31" customHeight="1" spans="1:26">
+      <c r="A4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>527</v>
+      </c>
+      <c r="J4" s="6"/>
+      <c r="K4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="T4" s="7">
+        <v>2</v>
+      </c>
+      <c r="U4" s="7">
+        <v>4</v>
+      </c>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7" t="s">
+        <v>531</v>
+      </c>
+      <c r="X4" s="7"/>
+      <c r="Y4" t="s">
+        <v>532</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24">
+      <c r="A5" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+    </row>
+    <row r="6" ht="60" customHeight="1" spans="1:26">
+      <c r="A6" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="E6" s="8"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>539</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="S6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="T6" s="7">
+        <v>4</v>
+      </c>
+      <c r="U6" s="7">
+        <v>3</v>
+      </c>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="X6" s="7"/>
+      <c r="Y6" t="s">
+        <v>524</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="7" ht="43.2" spans="1:26">
+      <c r="A7" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B7" s="8"/>
+      <c r="C7" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>545</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>546</v>
+      </c>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="M7" s="6"/>
+      <c r="N7" s="5" t="s">
+        <v>551</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="Q7" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="S7" s="8"/>
+      <c r="T7" s="7">
+        <v>3</v>
+      </c>
+      <c r="U7" s="7">
+        <v>5</v>
+      </c>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7" t="s">
+        <v>556</v>
+      </c>
+      <c r="X7" s="7"/>
+      <c r="Y7" t="s">
+        <v>557</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>558</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>